--- a/reactionsICs_w_species.xlsx
+++ b/reactionsICs_w_species.xlsx
@@ -583,7 +583,7 @@
     <t xml:space="preserve">SERCA</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5-37.5</t>
+    <t xml:space="preserve">1.5-100</t>
   </si>
   <si>
     <t xml:space="preserve">dolan,eundamrong</t>
@@ -860,10 +860,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="mmm\-yy"/>
-    <numFmt numFmtId="166" formatCode="d\-mmm"/>
+    <numFmt numFmtId="165" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="mmm\-yy"/>
+    <numFmt numFmtId="167" formatCode="d\-mmm"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -982,12 +983,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1007,11 +1012,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1031,11 +1036,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1146,7 +1151,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G132"/>
-  <sheetFormatPr defaultColWidth="11.0078125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="63.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.83"/>
@@ -1159,14 +1164,14 @@
       <c r="B1" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="D1" s="0" t="n">
+      <c r="D1" s="2" t="n">
         <f aca="false">B1/(60*10^(-9))</f>
         <v>2733.33333333333</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1177,14 +1182,14 @@
       <c r="B2" s="1" t="n">
         <v>0.0159</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="2" t="n">
         <f aca="false">B2/60</f>
         <v>0.000265</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1195,14 +1200,14 @@
       <c r="B3" s="1" t="n">
         <v>0.000167</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="2" t="n">
         <f aca="false">B3/(60*10^(-6))</f>
         <v>2.78333333333333</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1213,14 +1218,14 @@
       <c r="B4" s="1" t="n">
         <v>0.00017</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="2" t="n">
         <f aca="false">B4/(60*10^(-6))</f>
         <v>2.83333333333333</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1231,10 +1236,10 @@
       <c r="B5" s="1" t="n">
         <v>0.01682</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1245,7 +1250,7 @@
       <c r="B6" s="1" t="n">
         <v>0.000167</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="2" t="n">
         <f aca="false">B6/(60*10^(-6))</f>
         <v>2.78333333333333</v>
       </c>
@@ -1257,20 +1262,20 @@
       <c r="B7" s="1" t="n">
         <v>0.000159</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="2" t="n">
         <v>0.0168</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="2" t="n">
         <f aca="false">B7/(60*10^(-6))</f>
         <v>2.65</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="2" t="n">
         <f aca="false">C7/(60)</f>
         <v>0.00028</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="2" t="n">
         <f aca="false">C8/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1282,20 +1287,20 @@
       <c r="B9" s="1" t="n">
         <v>0.000158</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="2" t="n">
         <v>0.0165</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="2" t="n">
         <f aca="false">B9/(60*10^(-6))</f>
         <v>2.63333333333333</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="2" t="n">
         <f aca="false">C9/(60*10^(-9))</f>
         <v>275000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="2" t="n">
         <f aca="false">C10/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1307,11 +1312,11 @@
       <c r="B11" s="1" t="n">
         <v>0.000166</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="2" t="n">
         <f aca="false">B11/(60*10^(-6))</f>
         <v>2.76666666666667</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="2" t="n">
         <f aca="false">C11/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1323,7 +1328,7 @@
       <c r="B12" s="1" t="n">
         <v>0.0164</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="2" t="n">
         <f aca="false">C12/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1339,7 +1344,7 @@
         <f aca="false">B13/(60*10^(-6))</f>
         <v>2.85</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="2" t="n">
         <f aca="false">C13/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1355,7 +1360,7 @@
         <f aca="false">B14/(60*10^(-6))</f>
         <v>28.1666666666667</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="2" t="n">
         <f aca="false">C14/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1371,7 +1376,7 @@
         <f aca="false">B15/(60*10^(-12))</f>
         <v>2833333.33333333</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="2" t="n">
         <f aca="false">C15/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1384,7 +1389,7 @@
         <v>0.015</v>
       </c>
       <c r="D16" s="1"/>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="2" t="n">
         <f aca="false">C16/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1400,7 +1405,7 @@
         <f aca="false">B17/(60*10^(-12))</f>
         <v>28166666.6666667</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="2" t="n">
         <f aca="false">C17/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1416,7 +1421,7 @@
         <f aca="false">B18/(60*10^(-6))</f>
         <v>2.71666666666667</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="2" t="n">
         <f aca="false">C18/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1432,7 +1437,7 @@
         <f aca="false">B19/(60*10^(-6))</f>
         <v>0.55</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="2" t="n">
         <f aca="false">C19/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1448,7 +1453,7 @@
         <f aca="false">B20/(60*10^(-6))</f>
         <v>2.76666666666667</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="2" t="n">
         <f aca="false">C20/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1460,21 +1465,21 @@
       <c r="B21" s="1" t="n">
         <v>0.000165</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21" s="2" t="n">
         <v>0.0168</v>
       </c>
       <c r="D21" s="1" t="n">
         <f aca="false">B21/(60*10^(-6))</f>
         <v>2.75</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21" s="2" t="n">
         <f aca="false">C21/(60*10^(-9))</f>
         <v>280000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D22" s="1"/>
-      <c r="E22" s="0" t="n">
+      <c r="E22" s="2" t="n">
         <f aca="false">C22/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1486,7 +1491,7 @@
       <c r="B23" s="1" t="n">
         <v>0.000185</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E23" s="2" t="n">
         <f aca="false">C23/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1498,7 +1503,7 @@
       <c r="B24" s="1" t="n">
         <v>3.5E-005</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24" s="2" t="n">
         <f aca="false">C24/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1510,7 +1515,7 @@
       <c r="B25" s="1" t="n">
         <v>0.082</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E25" s="2" t="n">
         <f aca="false">C25/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1522,7 +1527,7 @@
       <c r="B26" s="1" t="n">
         <v>0.00168</v>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="E26" s="2" t="n">
         <f aca="false">C26/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1534,11 +1539,11 @@
       <c r="B27" s="1" t="n">
         <v>0.0166</v>
       </c>
-      <c r="D27" s="0" t="n">
+      <c r="D27" s="2" t="n">
         <f aca="false">B27/(60*10^(-6))</f>
         <v>276.666666666667</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27" s="2" t="n">
         <f aca="false">C27/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1550,7 +1555,7 @@
       <c r="B28" s="1" t="n">
         <v>0.0167</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E28" s="2" t="n">
         <f aca="false">C28/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1562,7 +1567,7 @@
       <c r="B29" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E29" s="2" t="n">
         <f aca="false">C29/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1574,11 +1579,11 @@
       <c r="B30" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="D30" s="0" t="n">
+      <c r="D30" s="2" t="n">
         <f aca="false">B30/(60*10^(-6))</f>
         <v>283.333333333333</v>
       </c>
-      <c r="E30" s="0" t="n">
+      <c r="E30" s="2" t="n">
         <f aca="false">C30/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1590,11 +1595,11 @@
       <c r="B31" s="1" t="n">
         <v>1.7E-006</v>
       </c>
-      <c r="D31" s="0" t="n">
+      <c r="D31" s="2" t="n">
         <f aca="false">B31/(60*10^(-6))</f>
         <v>0.0283333333333333</v>
       </c>
-      <c r="E31" s="0" t="n">
+      <c r="E31" s="2" t="n">
         <f aca="false">C31/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1606,11 +1611,11 @@
       <c r="B32" s="1" t="n">
         <v>2E-006</v>
       </c>
-      <c r="D32" s="0" t="n">
+      <c r="D32" s="2" t="n">
         <f aca="false">B32/(60*10^(-6))</f>
         <v>0.0333333333333333</v>
       </c>
-      <c r="E32" s="0" t="n">
+      <c r="E32" s="2" t="n">
         <f aca="false">C32/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1622,7 +1627,7 @@
       <c r="B33" s="1" t="n">
         <v>0.00016</v>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E33" s="2" t="n">
         <f aca="false">C33/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1634,11 +1639,11 @@
       <c r="B34" s="1" t="n">
         <v>0.014</v>
       </c>
-      <c r="D34" s="0" t="n">
+      <c r="D34" s="2" t="n">
         <f aca="false">B34/(60*10^(-6))</f>
         <v>233.333333333333</v>
       </c>
-      <c r="E34" s="0" t="n">
+      <c r="E34" s="2" t="n">
         <f aca="false">C34/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1650,7 +1655,7 @@
       <c r="B35" s="1" t="n">
         <v>0.00165</v>
       </c>
-      <c r="E35" s="0" t="n">
+      <c r="E35" s="2" t="n">
         <f aca="false">C35/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1662,11 +1667,11 @@
       <c r="B36" s="1" t="n">
         <v>0.00062</v>
       </c>
-      <c r="D36" s="0" t="n">
+      <c r="D36" s="2" t="n">
         <f aca="false">B36/(60*10^(-6))</f>
         <v>10.3333333333333</v>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E36" s="2" t="n">
         <f aca="false">C36/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1678,7 +1683,7 @@
       <c r="B37" s="1" t="n">
         <v>0.0178</v>
       </c>
-      <c r="E37" s="0" t="n">
+      <c r="E37" s="2" t="n">
         <f aca="false">C37/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1690,11 +1695,11 @@
       <c r="B38" s="1" t="n">
         <v>0.0152</v>
       </c>
-      <c r="D38" s="0" t="n">
+      <c r="D38" s="2" t="n">
         <f aca="false">B38/(60*10^(-6))</f>
         <v>253.333333333333</v>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E38" s="2" t="n">
         <f aca="false">C38/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1706,7 +1711,7 @@
       <c r="B39" s="1" t="n">
         <v>0.000193</v>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E39" s="2" t="n">
         <f aca="false">C39/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1718,11 +1723,11 @@
       <c r="B40" s="1" t="n">
         <v>0.02</v>
       </c>
-      <c r="D40" s="0" t="n">
+      <c r="D40" s="2" t="n">
         <f aca="false">B40/(60*10^(-6))</f>
         <v>333.333333333333</v>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E40" s="2" t="n">
         <f aca="false">C40/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1734,11 +1739,11 @@
       <c r="B41" s="1" t="n">
         <v>0.0159</v>
       </c>
-      <c r="D41" s="0" t="n">
+      <c r="D41" s="2" t="n">
         <f aca="false">B41/(60*10^(-6))</f>
         <v>265</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E41" s="2" t="n">
         <f aca="false">C41/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1750,11 +1755,11 @@
       <c r="B42" s="1" t="n">
         <v>0.00062</v>
       </c>
-      <c r="D42" s="0" t="n">
+      <c r="D42" s="2" t="n">
         <f aca="false">B42/(60*10^(-6))</f>
         <v>10.3333333333333</v>
       </c>
-      <c r="E42" s="0" t="n">
+      <c r="E42" s="2" t="n">
         <f aca="false">C42/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1766,11 +1771,11 @@
       <c r="B43" s="1" t="n">
         <v>0.00015</v>
       </c>
-      <c r="D43" s="0" t="n">
+      <c r="D43" s="2" t="n">
         <f aca="false">B43/(60*10^(-6))</f>
         <v>2.5</v>
       </c>
-      <c r="E43" s="0" t="n">
+      <c r="E43" s="2" t="n">
         <f aca="false">C43/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1782,20 +1787,20 @@
       <c r="B44" s="1" t="n">
         <v>0.000169</v>
       </c>
-      <c r="C44" s="0" t="n">
+      <c r="C44" s="2" t="n">
         <v>0.0154</v>
       </c>
-      <c r="D44" s="0" t="n">
+      <c r="D44" s="2" t="n">
         <f aca="false">B44/(60*10^(-6))</f>
         <v>2.81666666666667</v>
       </c>
-      <c r="E44" s="0" t="n">
+      <c r="E44" s="2" t="n">
         <f aca="false">C44/(60*10^(-9))</f>
         <v>256666.666666667</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E45" s="0" t="n">
+      <c r="E45" s="2" t="n">
         <f aca="false">C45/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1815,7 +1820,7 @@
       <c r="B47" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="E47" s="0" t="n">
+      <c r="E47" s="2" t="n">
         <f aca="false">C50/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1827,7 +1832,7 @@
       <c r="B48" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="E48" s="0" t="n">
+      <c r="E48" s="2" t="n">
         <f aca="false">C51/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1839,7 +1844,7 @@
       <c r="B49" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="E49" s="0" t="n">
+      <c r="E49" s="2" t="n">
         <f aca="false">C52/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1851,11 +1856,11 @@
       <c r="B50" s="1" t="n">
         <v>0.00014</v>
       </c>
-      <c r="D50" s="0" t="n">
+      <c r="D50" s="2" t="n">
         <f aca="false">B50/(60*10^(-6))</f>
         <v>2.33333333333333</v>
       </c>
-      <c r="E50" s="0" t="n">
+      <c r="E50" s="2" t="n">
         <f aca="false">C54/(60*10^(-9))</f>
         <v>253333.333333333</v>
       </c>
@@ -1867,11 +1872,11 @@
       <c r="B51" s="1" t="n">
         <v>1.67E-005</v>
       </c>
-      <c r="D51" s="0" t="n">
+      <c r="D51" s="2" t="n">
         <f aca="false">B51/(60*10^(-6))</f>
         <v>0.278333333333333</v>
       </c>
-      <c r="E51" s="0" t="n">
+      <c r="E51" s="2" t="n">
         <f aca="false">C55/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1883,7 +1888,7 @@
       <c r="B52" s="1" t="n">
         <v>0.0166</v>
       </c>
-      <c r="E52" s="0" t="n">
+      <c r="E52" s="2" t="n">
         <f aca="false">C56/(60*10^(-9))</f>
         <v>256666.666666667</v>
       </c>
@@ -1895,7 +1900,7 @@
       <c r="B53" s="1" t="n">
         <v>0.000165</v>
       </c>
-      <c r="E53" s="0" t="n">
+      <c r="E53" s="2" t="n">
         <f aca="false">C57/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1907,16 +1912,16 @@
       <c r="B54" s="1" t="n">
         <v>0.000177</v>
       </c>
-      <c r="C54" s="0" t="n">
+      <c r="C54" s="2" t="n">
         <v>0.0152</v>
       </c>
-      <c r="E54" s="0" t="n">
+      <c r="E54" s="2" t="n">
         <f aca="false">C58/(60*10^(-9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E55" s="0" t="n">
+      <c r="E55" s="2" t="n">
         <f aca="false">C59/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1928,16 +1933,16 @@
       <c r="B56" s="1" t="n">
         <v>0.00017</v>
       </c>
-      <c r="C56" s="0" t="n">
+      <c r="C56" s="2" t="n">
         <v>0.0154</v>
       </c>
-      <c r="E56" s="0" t="n">
+      <c r="E56" s="2" t="n">
         <f aca="false">C60/(60*10^(-9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E57" s="0" t="n">
+      <c r="E57" s="2" t="n">
         <f aca="false">C61/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1949,7 +1954,7 @@
       <c r="B58" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="E58" s="0" t="n">
+      <c r="E58" s="2" t="n">
         <f aca="false">C62/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1961,11 +1966,11 @@
       <c r="B59" s="1" t="n">
         <v>0.000188</v>
       </c>
-      <c r="D59" s="0" t="n">
+      <c r="D59" s="2" t="n">
         <f aca="false">B59/(60*10^(-6))</f>
         <v>3.13333333333333</v>
       </c>
-      <c r="E59" s="0" t="n">
+      <c r="E59" s="2" t="n">
         <f aca="false">C63/(60*10^(-9))</f>
         <v>78.3333333333333</v>
       </c>
@@ -1977,7 +1982,7 @@
       <c r="B60" s="1" t="n">
         <v>0.016</v>
       </c>
-      <c r="E60" s="0" t="n">
+      <c r="E60" s="2" t="n">
         <f aca="false">C64/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -1989,11 +1994,11 @@
       <c r="B61" s="1" t="n">
         <v>0.000193</v>
       </c>
-      <c r="D61" s="0" t="n">
+      <c r="D61" s="2" t="n">
         <f aca="false">B61/(60*10^(-6))</f>
         <v>3.21666666666667</v>
       </c>
-      <c r="E61" s="0" t="n">
+      <c r="E61" s="2" t="n">
         <f aca="false">C65/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2005,11 +2010,11 @@
       <c r="B62" s="1" t="n">
         <v>0.0002</v>
       </c>
-      <c r="D62" s="0" t="n">
+      <c r="D62" s="2" t="n">
         <f aca="false">B62/(60*10^(-6))</f>
         <v>3.33333333333333</v>
       </c>
-      <c r="E62" s="0" t="n">
+      <c r="E62" s="2" t="n">
         <f aca="false">C66/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2021,20 +2026,20 @@
       <c r="B63" s="1" t="n">
         <v>0.00019</v>
       </c>
-      <c r="C63" s="0" t="n">
+      <c r="C63" s="2" t="n">
         <v>4.7E-006</v>
       </c>
-      <c r="D63" s="0" t="n">
+      <c r="D63" s="2" t="n">
         <f aca="false">B63/(60*10^(-6))</f>
         <v>3.16666666666667</v>
       </c>
-      <c r="E63" s="0" t="n">
+      <c r="E63" s="2" t="n">
         <f aca="false">C67/(60*10^(-9))</f>
         <v>253333.333333333</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E64" s="0" t="n">
+      <c r="E64" s="2" t="n">
         <f aca="false">C68/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2046,11 +2051,11 @@
       <c r="B65" s="1" t="n">
         <v>0.000168</v>
       </c>
-      <c r="D65" s="0" t="n">
+      <c r="D65" s="2" t="n">
         <f aca="false">B65/(60*10^(-6))</f>
         <v>2.8</v>
       </c>
-      <c r="E65" s="0" t="n">
+      <c r="E65" s="2" t="n">
         <f aca="false">C69/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2062,11 +2067,11 @@
       <c r="B66" s="1" t="n">
         <v>5.6E-005</v>
       </c>
-      <c r="D66" s="0" t="n">
+      <c r="D66" s="2" t="n">
         <f aca="false">B66/(60*10^(-6))</f>
         <v>0.933333333333333</v>
       </c>
-      <c r="E66" s="0" t="n">
+      <c r="E66" s="2" t="n">
         <f aca="false">C70/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2078,20 +2083,20 @@
       <c r="B67" s="1" t="n">
         <v>0.00014</v>
       </c>
-      <c r="C67" s="0" t="n">
+      <c r="C67" s="2" t="n">
         <v>0.0152</v>
       </c>
-      <c r="D67" s="0" t="n">
+      <c r="D67" s="2" t="n">
         <f aca="false">B67/(60*10^(-6))</f>
         <v>2.33333333333333</v>
       </c>
-      <c r="E67" s="0" t="n">
+      <c r="E67" s="2" t="n">
         <f aca="false">C71/(60*10^(-9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E68" s="0" t="n">
+      <c r="E68" s="2" t="n">
         <f aca="false">C72/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2103,7 +2108,7 @@
       <c r="B69" s="1" t="n">
         <v>0.02</v>
       </c>
-      <c r="E69" s="0" t="n">
+      <c r="E69" s="2" t="n">
         <f aca="false">C73/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2115,7 +2120,7 @@
       <c r="B70" s="1" t="n">
         <v>0.0833</v>
       </c>
-      <c r="E70" s="0" t="n">
+      <c r="E70" s="2" t="n">
         <f aca="false">C74/(60*10^(-9))</f>
         <v>325000</v>
       </c>
@@ -2127,11 +2132,11 @@
       <c r="B71" s="1" t="n">
         <v>0.00021</v>
       </c>
-      <c r="D71" s="0" t="n">
+      <c r="D71" s="2" t="n">
         <f aca="false">B71/(60*10^(-6))</f>
         <v>3.5</v>
       </c>
-      <c r="E71" s="0" t="n">
+      <c r="E71" s="2" t="n">
         <f aca="false">C75/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2143,11 +2148,11 @@
       <c r="B72" s="1" t="n">
         <v>0.0188</v>
       </c>
-      <c r="D72" s="0" t="n">
+      <c r="D72" s="2" t="n">
         <f aca="false">B72/(60*10^(-6))</f>
         <v>313.333333333333</v>
       </c>
-      <c r="E72" s="0" t="n">
+      <c r="E72" s="2" t="n">
         <f aca="false">C76/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2159,7 +2164,7 @@
       <c r="B73" s="1" t="n">
         <v>0.0166</v>
       </c>
-      <c r="E73" s="0" t="n">
+      <c r="E73" s="2" t="n">
         <f aca="false">C77/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2171,20 +2176,20 @@
       <c r="B74" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="C74" s="0" t="n">
+      <c r="C74" s="2" t="n">
         <v>0.0195</v>
       </c>
-      <c r="D74" s="0" t="n">
+      <c r="D74" s="2" t="n">
         <f aca="false">B74/(60*10^(-6))</f>
         <v>33.3333333333333</v>
       </c>
-      <c r="E74" s="0" t="n">
+      <c r="E74" s="2" t="n">
         <f aca="false">C78/(60*10^(-9))</f>
         <v>316666.666666667</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E75" s="0" t="n">
+      <c r="E75" s="2" t="n">
         <f aca="false">C79/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2196,7 +2201,7 @@
       <c r="B76" s="1" t="n">
         <v>0.021</v>
       </c>
-      <c r="E76" s="0" t="n">
+      <c r="E76" s="2" t="n">
         <f aca="false">C80/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2208,11 +2213,11 @@
       <c r="B77" s="1" t="n">
         <v>3E-005</v>
       </c>
-      <c r="D77" s="0" t="n">
+      <c r="D77" s="2" t="n">
         <f aca="false">B77/(60*10^(-6))</f>
         <v>0.5</v>
       </c>
-      <c r="E77" s="0" t="n">
+      <c r="E77" s="2" t="n">
         <f aca="false">C81/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2224,20 +2229,20 @@
       <c r="B78" s="1" t="n">
         <v>0.00021</v>
       </c>
-      <c r="C78" s="0" t="n">
+      <c r="C78" s="2" t="n">
         <v>0.019</v>
       </c>
-      <c r="D78" s="0" t="n">
+      <c r="D78" s="2" t="n">
         <f aca="false">B78/(60*10^(-6))</f>
         <v>3.5</v>
       </c>
-      <c r="E78" s="0" t="n">
+      <c r="E78" s="2" t="n">
         <f aca="false">C82/(60*10^(-9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E79" s="0" t="n">
+      <c r="E79" s="2" t="n">
         <f aca="false">C83/(60*10^(-9))</f>
         <v>25666.6666666667</v>
       </c>
@@ -2249,11 +2254,11 @@
       <c r="B80" s="1" t="n">
         <v>0.0001667</v>
       </c>
-      <c r="D80" s="0" t="n">
+      <c r="D80" s="2" t="n">
         <f aca="false">B80/(60*10^(-6))</f>
         <v>2.77833333333333</v>
       </c>
-      <c r="E80" s="0" t="n">
+      <c r="E80" s="2" t="n">
         <f aca="false">C84/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2265,7 +2270,7 @@
       <c r="B81" s="1" t="n">
         <v>0.084</v>
       </c>
-      <c r="E81" s="0" t="n">
+      <c r="E81" s="2" t="n">
         <f aca="false">C85/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2277,7 +2282,7 @@
       <c r="B82" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="E82" s="0" t="n">
+      <c r="E82" s="2" t="n">
         <f aca="false">C86/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2289,20 +2294,20 @@
       <c r="B83" s="1" t="n">
         <v>0.000156</v>
       </c>
-      <c r="C83" s="0" t="n">
+      <c r="C83" s="2" t="n">
         <v>0.00154</v>
       </c>
-      <c r="D83" s="0" t="n">
+      <c r="D83" s="2" t="n">
         <f aca="false">B83/(60*10^(-6))</f>
         <v>2.6</v>
       </c>
-      <c r="E83" s="0" t="n">
+      <c r="E83" s="2" t="n">
         <f aca="false">C87/(60*10^(-9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E84" s="0" t="n">
+      <c r="E84" s="2" t="n">
         <f aca="false">C88/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2314,11 +2319,11 @@
       <c r="B85" s="1" t="n">
         <v>0.000167</v>
       </c>
-      <c r="D85" s="0" t="n">
+      <c r="D85" s="2" t="n">
         <f aca="false">B85/(60*10^(-6))</f>
         <v>2.78333333333333</v>
       </c>
-      <c r="E85" s="0" t="n">
+      <c r="E85" s="2" t="n">
         <f aca="false">C89/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2330,11 +2335,11 @@
       <c r="B86" s="1" t="n">
         <v>0.000165</v>
       </c>
-      <c r="D86" s="0" t="n">
+      <c r="D86" s="2" t="n">
         <f aca="false">B86/(60*10^(-6))</f>
         <v>2.75</v>
       </c>
-      <c r="E86" s="0" t="n">
+      <c r="E86" s="2" t="n">
         <f aca="false">C90/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2346,7 +2351,7 @@
       <c r="B87" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="E87" s="0" t="n">
+      <c r="E87" s="2" t="n">
         <f aca="false">C91/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2358,7 +2363,7 @@
       <c r="B88" s="1" t="n">
         <v>0.000155</v>
       </c>
-      <c r="E88" s="0" t="n">
+      <c r="E88" s="2" t="n">
         <f aca="false">C92/(60*10^(-9))</f>
         <v>300000</v>
       </c>
@@ -2370,11 +2375,11 @@
       <c r="B89" s="1" t="n">
         <v>7E-005</v>
       </c>
-      <c r="D89" s="0" t="n">
+      <c r="D89" s="2" t="n">
         <f aca="false">B89/(60*10^(-6))</f>
         <v>1.16666666666667</v>
       </c>
-      <c r="E89" s="0" t="n">
+      <c r="E89" s="2" t="n">
         <f aca="false">C93/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2386,7 +2391,7 @@
       <c r="B90" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="E90" s="0" t="n">
+      <c r="E90" s="2" t="n">
         <f aca="false">C94/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2398,7 +2403,7 @@
       <c r="B91" s="1" t="n">
         <v>0.014</v>
       </c>
-      <c r="E91" s="0" t="n">
+      <c r="E91" s="2" t="n">
         <f aca="false">C95/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2410,16 +2415,16 @@
       <c r="B92" s="1" t="n">
         <v>0.016</v>
       </c>
-      <c r="C92" s="0" t="n">
+      <c r="C92" s="2" t="n">
         <v>0.018</v>
       </c>
-      <c r="E92" s="0" t="n">
+      <c r="E92" s="2" t="n">
         <f aca="false">C96/(60*10^(-9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E93" s="0" t="n">
+      <c r="E93" s="2" t="n">
         <f aca="false">C97/(60*10^(-9))</f>
         <v>166.666666666667</v>
       </c>
@@ -2431,7 +2436,7 @@
       <c r="B94" s="1" t="n">
         <v>0.0142</v>
       </c>
-      <c r="E94" s="0" t="n">
+      <c r="E94" s="2" t="n">
         <f aca="false">C98/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2443,11 +2448,11 @@
       <c r="B95" s="1" t="n">
         <v>0.000158</v>
       </c>
-      <c r="D95" s="0" t="n">
+      <c r="D95" s="2" t="n">
         <f aca="false">B95/(60*10^(-6))</f>
         <v>2.63333333333333</v>
       </c>
-      <c r="E95" s="0" t="n">
+      <c r="E95" s="2" t="n">
         <f aca="false">C99/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2459,7 +2464,7 @@
       <c r="B96" s="1" t="n">
         <v>0.0164</v>
       </c>
-      <c r="E96" s="0" t="n">
+      <c r="E96" s="2" t="n">
         <f aca="false">C100/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2471,20 +2476,20 @@
       <c r="B97" s="1" t="n">
         <v>0.000162</v>
       </c>
-      <c r="C97" s="0" t="n">
+      <c r="C97" s="2" t="n">
         <v>1E-005</v>
       </c>
-      <c r="D97" s="0" t="n">
+      <c r="D97" s="2" t="n">
         <f aca="false">B97/(60*10^(-6))</f>
         <v>2.7</v>
       </c>
-      <c r="E97" s="0" t="n">
+      <c r="E97" s="2" t="n">
         <f aca="false">C101/(60*10^(-9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E98" s="0" t="n">
+      <c r="E98" s="2" t="n">
         <f aca="false">C102/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2496,7 +2501,7 @@
       <c r="B99" s="1" t="n">
         <v>0.018</v>
       </c>
-      <c r="E99" s="0" t="n">
+      <c r="E99" s="2" t="n">
         <f aca="false">C103/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2508,7 +2513,7 @@
       <c r="B100" s="1" t="n">
         <v>0.018</v>
       </c>
-      <c r="E100" s="0" t="n">
+      <c r="E100" s="2" t="n">
         <f aca="false">C104/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2520,7 +2525,7 @@
       <c r="B101" s="1" t="n">
         <v>0.0162</v>
       </c>
-      <c r="E101" s="0" t="n">
+      <c r="E101" s="2" t="n">
         <f aca="false">C105/(60*10^(-9))</f>
         <v>833333.333333333</v>
       </c>
@@ -2532,11 +2537,11 @@
       <c r="B102" s="1" t="n">
         <v>0.000166</v>
       </c>
-      <c r="D102" s="0" t="n">
+      <c r="D102" s="2" t="n">
         <f aca="false">B102/(60*10^(-6))</f>
         <v>2.76666666666667</v>
       </c>
-      <c r="E102" s="0" t="n">
+      <c r="E102" s="2" t="n">
         <f aca="false">C106/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2548,11 +2553,11 @@
       <c r="B103" s="1" t="n">
         <v>0.000157</v>
       </c>
-      <c r="D103" s="0" t="n">
+      <c r="D103" s="2" t="n">
         <f aca="false">B103/(60*10^(-6))</f>
         <v>2.61666666666667</v>
       </c>
-      <c r="E103" s="0" t="n">
+      <c r="E103" s="2" t="n">
         <f aca="false">C107/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2564,7 +2569,7 @@
       <c r="B104" s="1" t="n">
         <v>0.0085</v>
       </c>
-      <c r="E104" s="0" t="n">
+      <c r="E104" s="2" t="n">
         <f aca="false">C108/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2576,20 +2581,20 @@
       <c r="B105" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="C105" s="0" t="n">
+      <c r="C105" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="D105" s="0" t="n">
+      <c r="D105" s="2" t="n">
         <f aca="false">B105/(60*10^(-6))</f>
         <v>16.6666666666667</v>
       </c>
-      <c r="E105" s="0" t="n">
+      <c r="E105" s="2" t="n">
         <f aca="false">C109/(60*10^(-9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E106" s="0" t="n">
+      <c r="E106" s="2" t="n">
         <f aca="false">C110/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2601,7 +2606,7 @@
       <c r="B107" s="1" t="n">
         <v>0.0072</v>
       </c>
-      <c r="E107" s="0" t="n">
+      <c r="E107" s="2" t="n">
         <f aca="false">C111/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2613,7 +2618,7 @@
       <c r="B108" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="E108" s="0" t="n">
+      <c r="E108" s="2" t="n">
         <f aca="false">C112/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2625,7 +2630,7 @@
       <c r="B109" s="1" t="n">
         <v>0.0166</v>
       </c>
-      <c r="E109" s="0" t="n">
+      <c r="E109" s="2" t="n">
         <f aca="false">C113/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2637,11 +2642,11 @@
       <c r="B110" s="1" t="n">
         <v>0.00017</v>
       </c>
-      <c r="D110" s="0" t="n">
+      <c r="D110" s="2" t="n">
         <f aca="false">B110/(60*10^(-6))</f>
         <v>2.83333333333333</v>
       </c>
-      <c r="E110" s="0" t="n">
+      <c r="E110" s="2" t="n">
         <f aca="false">C114/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2653,11 +2658,11 @@
       <c r="B111" s="1" t="n">
         <v>1.6E-006</v>
       </c>
-      <c r="D111" s="0" t="n">
+      <c r="D111" s="2" t="n">
         <f aca="false">B111/(60*10^(-6))</f>
         <v>0.0266666666666667</v>
       </c>
-      <c r="E111" s="0" t="n">
+      <c r="E111" s="2" t="n">
         <f aca="false">C115/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2669,7 +2674,7 @@
       <c r="B112" s="1" t="n">
         <v>0.00017</v>
       </c>
-      <c r="E112" s="0" t="n">
+      <c r="E112" s="2" t="n">
         <f aca="false">C116/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2681,11 +2686,11 @@
       <c r="B113" s="1" t="n">
         <v>0.024</v>
       </c>
-      <c r="D113" s="0" t="n">
+      <c r="D113" s="2" t="n">
         <f aca="false">B113/(60*10^(-6))</f>
         <v>400</v>
       </c>
-      <c r="E113" s="0" t="n">
+      <c r="E113" s="2" t="n">
         <f aca="false">C117/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2697,7 +2702,7 @@
       <c r="B114" s="1" t="n">
         <v>0.022</v>
       </c>
-      <c r="E114" s="0" t="n">
+      <c r="E114" s="2" t="n">
         <f aca="false">C118/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2709,11 +2714,11 @@
       <c r="B115" s="1" t="n">
         <v>0.0189</v>
       </c>
-      <c r="D115" s="0" t="n">
+      <c r="D115" s="2" t="n">
         <f aca="false">B115/(60*10^(-6))</f>
         <v>315</v>
       </c>
-      <c r="E115" s="0" t="n">
+      <c r="E115" s="2" t="n">
         <f aca="false">C119/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2725,7 +2730,7 @@
       <c r="B116" s="1" t="n">
         <v>0.0176</v>
       </c>
-      <c r="E116" s="0" t="n">
+      <c r="E116" s="2" t="n">
         <f aca="false">C120/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2737,11 +2742,11 @@
       <c r="B117" s="1" t="n">
         <v>0.0155</v>
       </c>
-      <c r="D117" s="0" t="n">
+      <c r="D117" s="2" t="n">
         <f aca="false">B117/(60*10^(-6))</f>
         <v>258.333333333333</v>
       </c>
-      <c r="E117" s="0" t="n">
+      <c r="E117" s="2" t="n">
         <f aca="false">C121/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2753,11 +2758,11 @@
       <c r="B118" s="1" t="n">
         <v>0.000161</v>
       </c>
-      <c r="D118" s="0" t="n">
+      <c r="D118" s="2" t="n">
         <f aca="false">B118/(60*10^(-6))</f>
         <v>2.68333333333333</v>
       </c>
-      <c r="E118" s="0" t="n">
+      <c r="E118" s="2" t="n">
         <f aca="false">C122/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2769,11 +2774,11 @@
       <c r="B119" s="1" t="n">
         <v>0.000172</v>
       </c>
-      <c r="D119" s="0" t="n">
+      <c r="D119" s="2" t="n">
         <f aca="false">B119/(60*10^(-6))</f>
         <v>2.86666666666667</v>
       </c>
-      <c r="E119" s="0" t="n">
+      <c r="E119" s="2" t="n">
         <f aca="false">C123/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2785,11 +2790,11 @@
       <c r="B120" s="1" t="n">
         <v>0.000169</v>
       </c>
-      <c r="D120" s="0" t="n">
+      <c r="D120" s="2" t="n">
         <f aca="false">B120/(60*10^(-6))</f>
         <v>2.81666666666667</v>
       </c>
-      <c r="E120" s="0" t="n">
+      <c r="E120" s="2" t="n">
         <f aca="false">C124/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2801,11 +2806,11 @@
       <c r="B121" s="1" t="n">
         <v>0.031</v>
       </c>
-      <c r="D121" s="0" t="n">
+      <c r="D121" s="2" t="n">
         <f aca="false">B121/(60*10^(-6))</f>
         <v>516.666666666667</v>
       </c>
-      <c r="E121" s="0" t="n">
+      <c r="E121" s="2" t="n">
         <f aca="false">C125/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2817,11 +2822,11 @@
       <c r="B122" s="1" t="n">
         <v>0.000161</v>
       </c>
-      <c r="D122" s="0" t="n">
+      <c r="D122" s="2" t="n">
         <f aca="false">B122/(60*10^(-6))</f>
         <v>2.68333333333333</v>
       </c>
-      <c r="E122" s="0" t="n">
+      <c r="E122" s="2" t="n">
         <f aca="false">C126/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2833,7 +2838,7 @@
       <c r="B123" s="1" t="n">
         <v>0.0159</v>
       </c>
-      <c r="E123" s="0" t="n">
+      <c r="E123" s="2" t="n">
         <f aca="false">C127/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2845,11 +2850,11 @@
       <c r="B124" s="1" t="n">
         <v>0.0034</v>
       </c>
-      <c r="D124" s="0" t="n">
+      <c r="D124" s="2" t="n">
         <f aca="false">B124/(60*10^(-6))</f>
         <v>56.6666666666667</v>
       </c>
-      <c r="E124" s="0" t="n">
+      <c r="E124" s="2" t="n">
         <f aca="false">C128/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2861,7 +2866,7 @@
       <c r="B125" s="1" t="n">
         <v>0.087</v>
       </c>
-      <c r="E125" s="0" t="n">
+      <c r="E125" s="2" t="n">
         <f aca="false">C129/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2873,11 +2878,11 @@
       <c r="B126" s="1" t="n">
         <v>0.00052</v>
       </c>
-      <c r="D126" s="0" t="n">
+      <c r="D126" s="2" t="n">
         <f aca="false">B126/(60*10^(-6))</f>
         <v>8.66666666666667</v>
       </c>
-      <c r="E126" s="0" t="n">
+      <c r="E126" s="2" t="n">
         <f aca="false">C130/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2889,7 +2894,7 @@
       <c r="B127" s="1" t="n">
         <v>0.078</v>
       </c>
-      <c r="E127" s="0" t="n">
+      <c r="E127" s="2" t="n">
         <f aca="false">C131/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2901,11 +2906,11 @@
       <c r="B128" s="1" t="n">
         <v>2.6E-005</v>
       </c>
-      <c r="D128" s="0" t="n">
+      <c r="D128" s="2" t="n">
         <f aca="false">B128/(60*10^(-6))</f>
         <v>0.433333333333333</v>
       </c>
-      <c r="E128" s="0" t="n">
+      <c r="E128" s="2" t="n">
         <f aca="false">C132/(60*10^(-9))</f>
         <v>0</v>
       </c>
@@ -2917,7 +2922,7 @@
       <c r="B129" s="1" t="n">
         <v>5.3E-005</v>
       </c>
-      <c r="D129" s="0" t="n">
+      <c r="D129" s="2" t="n">
         <f aca="false">B129/(60*10^(-6))</f>
         <v>0.883333333333333</v>
       </c>
@@ -2962,972 +2967,973 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T56"/>
-  <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:T1048576"/>
+  <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="12.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="12.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="9.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="12.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="2" width="12.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="12.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="12.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="12.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="4" t="n">
+      <c r="B1" s="5" t="n">
         <v>1.4434</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="R2" s="0" t="s">
+      <c r="R2" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="S2" s="0" t="s">
+      <c r="S2" s="2" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="H3" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="P3" s="0" t="n">
+      <c r="H3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="P3" s="2" t="n">
         <f aca="false">200/(R3*S3)</f>
         <v>6.66666666666667E-014</v>
       </c>
-      <c r="Q3" s="0" t="s">
+      <c r="Q3" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="R3" s="0" t="n">
+      <c r="R3" s="2" t="n">
         <f aca="false">5*10^(-9)</f>
         <v>5E-009</v>
       </c>
-      <c r="S3" s="0" t="n">
+      <c r="S3" s="2" t="n">
         <f aca="false">6*10^(23)</f>
         <v>6E+023</v>
       </c>
-      <c r="T3" s="0" t="n">
+      <c r="T3" s="2" t="n">
         <f aca="false">R3*S3</f>
         <v>3000000000000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G4" s="0" t="s">
+      <c r="C4" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="H4" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="P4" s="0" t="n">
+      <c r="H4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="P4" s="2" t="n">
         <f aca="false">P3*1000</f>
         <v>6.66666666666667E-011</v>
       </c>
-      <c r="Q4" s="0" t="s">
+      <c r="Q4" s="2" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <f aca="false">2*10^6</f>
         <v>2000000</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="H5" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="P5" s="0" t="n">
+      <c r="H5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="P5" s="2" t="n">
         <f aca="false">P4*10^9</f>
         <v>0.0666666666666667</v>
       </c>
-      <c r="Q5" s="0" t="s">
+      <c r="Q5" s="2" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="2" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="C7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="2" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9" s="0" t="s">
+      <c r="C9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="2" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="C10" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="C11" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C12" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D12" s="0" t="s">
+      <c r="C12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="B13" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="0" t="s">
+      <c r="C14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="I14" s="0" t="s">
+      <c r="I14" s="2" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="3" t="n">
         <f aca="false">14/VNa*10^9</f>
         <v>4.66666666666667E-006</v>
       </c>
-      <c r="C15" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="I15" s="0" t="s">
+      <c r="I15" s="2" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="3" t="n">
         <f aca="false">10^5/VNa*10^9</f>
         <v>0.0333333333333333</v>
       </c>
-      <c r="C16" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D16" s="0" t="s">
+      <c r="C16" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="2" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C17" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D17" s="0" t="s">
+      <c r="C17" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C18" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D18" s="0" t="s">
+      <c r="C18" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="11" t="n">
         <v>205</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D19" s="9" t="s">
+      <c r="C19" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D20" s="0" t="s">
+      <c r="C20" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="G20" s="0" t="s">
+      <c r="G20" s="2" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C21" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D21" s="0" t="s">
+      <c r="C21" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G21" s="11"/>
+      <c r="G21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="C22" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="G22" s="12" t="n">
         <f aca="false">G21/VNa*10^9</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="C23" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D23" s="0" t="s">
+      <c r="C23" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="3" t="n">
         <v>64.572</v>
       </c>
-      <c r="C24" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" s="0" t="s">
+      <c r="C24" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C25" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="C25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="C26" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D26" s="5" t="s">
+      <c r="C26" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="E26" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" s="2" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C27" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D27" s="0" t="s">
+      <c r="C27" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C28" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D28" s="0" t="s">
+      <c r="C28" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C29" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D29" s="0" t="s">
+      <c r="C29" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="C30" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D30" s="5" t="s">
+      <c r="C30" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="6" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D31" s="0" t="s">
+      <c r="B31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D32" s="8" t="s">
+      <c r="C32" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C33" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D33" s="5" t="s">
+      <c r="C33" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" s="2" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C34" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D34" s="0" t="s">
+      <c r="C34" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B35" s="2" t="n">
+      <c r="B35" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C35" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D35" s="0" t="s">
+      <c r="C35" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="C36" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D36" s="0" t="s">
+      <c r="C36" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C37" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="C37" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="E37" s="0" t="s">
+      <c r="E37" s="2" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C38" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D38" s="8" t="s">
+      <c r="C38" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="9" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="B39" s="14" t="n">
+      <c r="B39" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D39" s="8" t="s">
+      <c r="C39" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="9" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C40" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D40" s="5" t="s">
+      <c r="C40" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C41" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D41" s="5" t="s">
+      <c r="C41" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D41" s="6" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C42" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D42" s="0" t="s">
+      <c r="C42" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="C43" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D43" s="15" t="s">
+      <c r="C43" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="E43" s="8"/>
+      <c r="E43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C44" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D44" s="0" t="s">
+      <c r="C44" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B45" s="3" t="n">
         <f aca="false">27000/VNa*10^9</f>
         <v>0.009</v>
       </c>
-      <c r="C45" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D45" s="5" t="s">
+      <c r="C45" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D45" s="6" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C46" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D46" s="5" t="s">
+      <c r="C46" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" s="2" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B47" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="C47" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D47" s="5" t="s">
+      <c r="C47" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D47" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E47" s="0" t="s">
+      <c r="E47" s="2" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="B48" s="14" t="n">
+      <c r="B48" s="15" t="n">
         <v>300</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D48" s="8" t="s">
+      <c r="C48" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="9" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="B49" s="18" t="n">
+      <c r="B49" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="C49" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="D49" s="19" t="s">
+      <c r="C49" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="D49" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="18" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B50" s="2" t="n">
+      <c r="B50" s="3" t="n">
         <f aca="false">3000/VNa*10^9</f>
         <v>0.001</v>
       </c>
-      <c r="C50" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D50" s="0" t="s">
+      <c r="C50" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D51" s="8" t="s">
+      <c r="C51" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="E51" s="8"/>
+      <c r="E51" s="9"/>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B52" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="C52" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D52" s="0" t="s">
+      <c r="C52" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E52" s="0" t="s">
+      <c r="E52" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="F52" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="G52" s="0" t="s">
+      <c r="G52" s="2" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B53" s="2" t="n">
+      <c r="B53" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="C53" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D53" s="0" t="s">
+      <c r="C53" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D54" s="0" t="s">
+      <c r="C54" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B55" s="2" t="n">
+      <c r="B55" s="3" t="n">
         <f aca="false">P5</f>
         <v>0.0666666666666667</v>
       </c>
-      <c r="C55" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="D55" s="5" t="s">
+      <c r="C55" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D55" s="6" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C56" s="0" t="s">
-        <v>129</v>
-      </c>
-    </row>
+      <c r="C56" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D1" r:id="rId1" display="Neumann"/>
@@ -3977,317 +3983,317 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="2" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="n">
+      <c r="A2" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="n">
+      <c r="B2" s="21" t="n">
         <v>0.057708371</v>
       </c>
-      <c r="C2" s="20" t="n">
+      <c r="C2" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="20" t="n">
+      <c r="D2" s="21" t="n">
         <v>0.06659417</v>
       </c>
-      <c r="E2" s="20" t="n">
+      <c r="E2" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="20" t="n">
+      <c r="F2" s="21" t="n">
         <v>0.113762439</v>
       </c>
-      <c r="G2" s="20" t="n">
+      <c r="G2" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="20" t="n">
+      <c r="H2" s="21" t="n">
         <v>0.052919863</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="n">
+      <c r="A3" s="21" t="n">
         <v>0.328824908</v>
       </c>
-      <c r="B3" s="20" t="n">
+      <c r="B3" s="21" t="n">
         <v>0.033738787</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="C3" s="21" t="n">
         <v>0.736130795</v>
       </c>
-      <c r="D3" s="20" t="n">
+      <c r="D3" s="21" t="n">
         <v>0.012741815</v>
       </c>
-      <c r="E3" s="20" t="n">
+      <c r="E3" s="21" t="n">
         <v>5.874494001</v>
       </c>
-      <c r="F3" s="20" t="n">
+      <c r="F3" s="21" t="n">
         <v>0.151931424</v>
       </c>
-      <c r="G3" s="20" t="n">
+      <c r="G3" s="21" t="n">
         <v>2.678453256</v>
       </c>
-      <c r="H3" s="20" t="n">
+      <c r="H3" s="21" t="n">
         <v>0.196272068</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="n">
+      <c r="A4" s="21" t="n">
         <v>0.245583783</v>
       </c>
-      <c r="B4" s="20" t="n">
+      <c r="B4" s="21" t="n">
         <v>0.0124392</v>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="21" t="n">
         <v>0.642196733</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="21" t="n">
         <v>0.041460076</v>
       </c>
-      <c r="E4" s="20" t="n">
+      <c r="E4" s="21" t="n">
         <v>12.00608973</v>
       </c>
-      <c r="F4" s="20" t="n">
+      <c r="F4" s="21" t="n">
         <v>0.225558969</v>
       </c>
-      <c r="G4" s="20" t="n">
+      <c r="G4" s="21" t="n">
         <v>2.326520958</v>
       </c>
-      <c r="H4" s="20" t="n">
+      <c r="H4" s="21" t="n">
         <v>0.21323128</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="n">
+      <c r="A5" s="21" t="n">
         <v>0.406145533</v>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" s="21" t="n">
         <v>0.077622761</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="21" t="n">
         <v>0.824566071</v>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="21" t="n">
         <v>0.006662436</v>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="21" t="n">
         <v>9.293454641</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="21" t="n">
         <v>0.076389622</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="21" t="n">
         <v>1.77141628</v>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="21" t="n">
         <v>0.112561902</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="21" t="n">
         <v>0.452013067</v>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="21" t="n">
         <v>0.060164088</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="21" t="n">
         <v>0.616804233</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="21" t="n">
         <v>0.025687951</v>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="21" t="n">
         <v>6.352155462</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="21" t="n">
         <v>0.113317853</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="21" t="n">
         <v>2.199335445</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="21" t="n">
         <v>0.121303907</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="21" t="n">
         <v>0.511601478</v>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="21" t="n">
         <v>0.011503304</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="21" t="n">
         <v>0.547645692</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="21" t="n">
         <v>0.005493335</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="21" t="n">
         <v>6.358520131</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="21" t="n">
         <v>0.254350078</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="21" t="n">
         <v>2.848776153</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="21" t="n">
         <v>0.095341645</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="21" t="n">
         <v>0.199496967</v>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="21" t="n">
         <v>0.045938233</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="21" t="n">
         <v>0.506191749</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="21" t="n">
         <v>0.011392007</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="21" t="n">
         <v>9.346884844</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="21" t="n">
         <v>0.340815117</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="21" t="n">
         <v>2.084090103</v>
       </c>
-      <c r="H8" s="20" t="n">
+      <c r="H8" s="21" t="n">
         <v>0.189995246</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="21" t="n">
         <v>0.163379163</v>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="21" t="n">
         <v>0.109206759</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="21" t="n">
         <v>0.510822206</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="21" t="n">
         <v>0.02937321</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="21" t="n">
         <v>9.580699906</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="21" t="n">
         <v>1.162044437</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="21" t="n">
         <v>1.700446987</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="21" t="n">
         <v>0.077889356</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="21" t="n">
         <v>0.116531919</v>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="21" t="n">
         <v>0.042836171</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="21" t="n">
         <v>0.628275564</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="21" t="n">
         <v>0.001210989</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="21" t="n">
         <v>11.71887078</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="21" t="n">
         <v>0.966047945</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="21" t="n">
         <v>3.545101178</v>
       </c>
-      <c r="H10" s="20" t="n">
+      <c r="H10" s="21" t="n">
         <v>0.312004383</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="n">
+      <c r="A11" s="21" t="n">
         <v>0.145393099</v>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="21" t="n">
         <v>0.100218</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="21" t="n">
         <v>0.594305875</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="21" t="n">
         <v>0.06340267</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="21" t="n">
         <v>4.616744267</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="21" t="n">
         <v>0.178812298</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="21" t="n">
         <v>4.32653867</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="21" t="n">
         <v>0.126669768</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="21" t="n">
         <v>0.180639585</v>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="21" t="n">
         <v>0.05223528</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="21" t="n">
         <v>0.625180698</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>0.05062999</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="21" t="n">
         <v>3.711634044</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="21" t="n">
         <v>0.285834693</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="21" t="n">
         <v>2.289979681</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="21" t="n">
         <v>0.151026932</v>
       </c>
     </row>
